--- a/folib-web-core/src/main/resources/template/exceedSizeStorageTemplate.xlsx
+++ b/folib-web-core/src/main/resources/template/exceedSizeStorageTemplate.xlsx
@@ -4,22 +4,38 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15320"/>
+    <workbookView windowWidth="28000" windowHeight="13260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>存储空间存储额度告警</t>
   </si>
   <si>
     <t>所属存储空间</t>
+  </si>
+  <si>
+    <t>所属仓库</t>
   </si>
   <si>
     <t>存储配额（TB）</t>
@@ -32,6 +48,9 @@
   </si>
   <si>
     <t>{.storageId}</t>
+  </si>
+  <si>
+    <t>{.repositoryId}</t>
   </si>
   <si>
     <t>{.storageSize}</t>
@@ -982,15 +1001,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5961538461538" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.9134615384615" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.0288461538462" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8365384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.6634615384615" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.5865384615385" style="1" customWidth="1"/>
+    <col min="2" max="3" width="26.9134615384615" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.0288461538462" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.8365384615385" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.6634615384615" style="1" customWidth="1"/>
+    <col min="7" max="7" width="43.5865384615385" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1">
@@ -998,7 +1017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1011,24 +1030,30 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/folib-web-core/src/main/resources/template/exceedSizeStorageTemplate.xlsx
+++ b/folib-web-core/src/main/resources/template/exceedSizeStorageTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="13260"/>
+    <workbookView windowHeight="15480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,10 @@
     <t>所属仓库</t>
   </si>
   <si>
-    <t>存储配额（TB）</t>
+    <t>存储配额（GB）</t>
   </si>
   <si>
-    <t>已使用存储（TB）</t>
+    <t>已使用存储（GB）</t>
   </si>
   <si>
     <t>已使用占比（%）</t>
